--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487849_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487849_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9568</v>
+        <v>8.164</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7179</v>
+        <v>8.7471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2389</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1.6909</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6582</v>
+        <v>1.8654</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5281</v>
+        <v>1.5574</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1301</v>
+        <v>0.308</v>
       </c>
       <c r="V2" t="n">
         <v>5.0239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4588</v>
+        <v>4.4961</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2045</v>
+        <v>3.9483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2543</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0.4151</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8168</v>
+        <v>0.8542</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0092</v>
+        <v>0.753</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1924</v>
+        <v>0.1012</v>
       </c>
       <c r="V3" t="n">
         <v>0.9376</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2174</v>
+        <v>0.4882</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0192</v>
+        <v>4.2018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1983</v>
+        <v>-3.7136</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1131</v>
+        <v>2.8178</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1727</v>
+        <v>-0.8357</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2857</v>
+        <v>3.6535</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0192</v>
+        <v>4.7938</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0192</v>
+        <v>-0.1048</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.8985</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0939</v>
+        <v>-1.976</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1919</v>
+        <v>-0.731</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2857</v>
+        <v>-1.245</v>
       </c>
       <c r="P4" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1037</v>
+        <v>0.6111</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.4487</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1037</v>
+        <v>0.1625</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-3.1488</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-3.1488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3848</v>
+        <v>0.3833</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9511</v>
+        <v>0.1263</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3359</v>
+        <v>0.257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7097</v>
+        <v>0.1131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6288</v>
+        <v>-0.1727</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0809</v>
+        <v>0.2857</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8409</v>
+        <v>0.0192</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5558</v>
+        <v>0.0192</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2851</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1312</v>
+        <v>0.0939</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.927</v>
+        <v>-0.1919</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2042</v>
+        <v>0.2857</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.7055</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.2029</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4974</v>
+        <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3811</v>
+        <v>0.0621</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1643</v>
+        <v>0.1072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2167</v>
+        <v>-0.045</v>
       </c>
       <c r="V5" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5326</v>
+        <v>-0.1258</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3865</v>
+        <v>2.445</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.9191</v>
+        <v>-2.5708</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8178</v>
+        <v>1.7097</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8357</v>
+        <v>0.6288</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6535</v>
+        <v>1.0809</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7938</v>
+        <v>3.8409</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1048</v>
+        <v>1.5558</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8985</v>
+        <v>2.2851</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.976</v>
+        <v>-2.1312</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.731</v>
+        <v>-0.927</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.245</v>
+        <v>-1.2042</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-5.2029</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>2.4974</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4097</v>
+        <v>0.64</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3667</v>
+        <v>0.6582</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.043</v>
+        <v>-0.0182</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.1488</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.1488</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.1488</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FOREMAN JR</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.524</v>
+        <v>-0.7785</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4785</v>
+        <v>-0.6693</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9545</v>
+        <v>-0.1092</v>
       </c>
       <c r="G8" t="n">
-        <v>0.231</v>
+        <v>-1.0035</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3454</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5764</v>
+        <v>-1.072</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1363</v>
+        <v>-0.6686</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.676</v>
+        <v>-0.4457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5396</v>
+        <v>-0.2229</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3674</v>
+        <v>-0.3349</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3306</v>
+        <v>0.5142</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0367</v>
+        <v>-0.8491</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2487</v>
+        <v>1.2487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5063</v>
+        <v>-1.3775</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.261</v>
+        <v>-0.1276</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2453</v>
+        <v>-1.2499</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>D. FOREMAN JR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8325</v>
+        <v>-1.2025</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3122</v>
+        <v>-2.157</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5203</v>
+        <v>0.9545</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0035</v>
+        <v>0.231</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.3454</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.072</v>
+        <v>0.5764</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6686</v>
+        <v>-0.1363</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4457</v>
+        <v>-0.676</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2229</v>
+        <v>0.5396</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3349</v>
+        <v>0.3674</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5142</v>
+        <v>0.3306</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8491</v>
+        <v>0.0367</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2487</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.4315</v>
+        <v>-0.1848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7705</v>
+        <v>0.0605</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.661</v>
+        <v>-0.2453</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4122</v>
+        <v>-2.1506</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.121</v>
+        <v>-1.7192</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2912</v>
+        <v>-0.4314</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4947</v>
+        <v>-2.421</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3306</v>
+        <v>1.2047</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1641</v>
+        <v>-3.6257</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2239</v>
+        <v>-0.5878</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1063</v>
+        <v>1.3683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1176</v>
+        <v>-1.9562</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7186</v>
+        <v>-1.8332</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4369</v>
+        <v>-0.1636</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2817</v>
+        <v>-1.6696</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>2.7055</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1044</v>
+        <v>0.4567</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4658</v>
+        <v>0.593</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3614</v>
+        <v>-0.1363</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6275</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6445</v>
+        <v>-2.7821</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.213</v>
+        <v>-0.5496</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4314</v>
+        <v>-2.2325</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.421</v>
+        <v>-0.4947</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2047</v>
+        <v>-0.3306</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6257</v>
+        <v>-0.1641</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5878</v>
+        <v>0.2239</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3683</v>
+        <v>0.1063</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9562</v>
+        <v>0.1176</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8332</v>
+        <v>-0.7186</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1636</v>
+        <v>-0.4369</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6696</v>
+        <v>-0.2817</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7055</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0372</v>
+        <v>-0.2655</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1363</v>
+        <v>-0.3027</v>
       </c>
       <c r="V11" t="n">
+        <v>-1.3975</v>
+      </c>
+      <c r="W11" t="n">
         <v>0.23</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.3975</v>
-      </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3648</v>
+        <v>-3.2282</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.468</v>
+        <v>-2.3609</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0456</v>
@@ -1390,13 +1390,13 @@
         <v>0.4162</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6948</v>
+        <v>-0.5583</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3686</v>
+        <v>-0.3392</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.288599999999999</v>
+        <v>2.6149</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6213</v>
+        <v>11.9473</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.3324</v>
+        <v>-9.3325</v>
       </c>
       <c r="G13" t="n">
         <v>0.5719000000000003</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1639</v>
+        <v>2.163900000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-1.5921</v>
@@ -1444,10 +1444,10 @@
         <v>12.7794</v>
       </c>
       <c r="K13" t="n">
-        <v>5.145700000000001</v>
+        <v>5.1457</v>
       </c>
       <c r="L13" t="n">
-        <v>7.633299999999999</v>
+        <v>7.6333</v>
       </c>
       <c r="M13" t="n">
         <v>-12.2074</v>
@@ -1468,16 +1468,16 @@
         <v>15.6087</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5692</v>
+        <v>1.8953</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4769</v>
+        <v>3.8033</v>
       </c>
       <c r="U13" t="n">
         <v>-1.9078</v>
       </c>
       <c r="V13" t="n">
-        <v>2.229000000000001</v>
+        <v>2.229</v>
       </c>
       <c r="W13" t="n">
         <v>13.0552</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7514</v>
+        <v>6.6507</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0547</v>
+        <v>7.6976</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3033</v>
+        <v>-1.0469</v>
       </c>
       <c r="G14" t="n">
         <v>2.8536</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4235</v>
+        <v>-0.5242</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.162</v>
+        <v>-0.5191</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2616</v>
+        <v>-0.0052</v>
       </c>
       <c r="V14" t="n">
         <v>2.4483</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8901</v>
+        <v>2.1209</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1511</v>
+        <v>3.2938</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.261</v>
+        <v>-1.1729</v>
       </c>
       <c r="G15" t="n">
         <v>1.8708</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2513</v>
+        <v>0.4821</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5807</v>
+        <v>0.7235</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3294</v>
+        <v>-0.2414</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1051</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0145</v>
+        <v>1.9137</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8146</v>
+        <v>2.6003</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8001</v>
+        <v>-0.6866</v>
       </c>
       <c r="G16" t="n">
         <v>4.3075</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0848</v>
+        <v>-0.1856</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4658</v>
+        <v>0.2515</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5506</v>
+        <v>-0.4371</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2135</v>
+        <v>0.6865</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8805</v>
+        <v>3.5591</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.667</v>
+        <v>-2.8725</v>
       </c>
       <c r="G17" t="n">
         <v>0.0429</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9812</v>
+        <v>0.4542</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8539</v>
+        <v>0.5325</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1273</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.8137</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4204</v>
+        <v>-0.0693</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8979</v>
+        <v>0.1478</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4774</v>
+        <v>-0.2171</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3378</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9851</v>
+        <v>0.4953</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6212</v>
+        <v>0.8711</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6361</v>
+        <v>-0.3758</v>
       </c>
       <c r="V18" t="n">
         <v>1.3975</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8535</v>
+        <v>-0.4733</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7865</v>
+        <v>-0.465</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.067</v>
+        <v>-0.0083</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7621</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.2888</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1305</v>
+        <v>0.191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.146</v>
+        <v>-1.0071</v>
       </c>
       <c r="E20" t="n">
         <v>0.7667</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9128</v>
+        <v>-1.7738</v>
       </c>
       <c r="G20" t="n">
         <v>2.8757</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3836</v>
+        <v>-0.2447</v>
       </c>
       <c r="T20" t="n">
         <v>-0.37</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0136</v>
+        <v>0.1253</v>
       </c>
       <c r="V20" t="n">
         <v>-2.8056</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7425</v>
+        <v>-2.1733</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6987</v>
+        <v>-1.2931</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0439</v>
+        <v>-0.8802</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5707</v>
+        <v>-0.7937</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5542</v>
+        <v>-0.6459</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0164</v>
+        <v>-0.1478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4925</v>
+        <v>-0.2628</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4354</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0572</v>
+        <v>0.7054</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0782</v>
+        <v>-0.5308</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1189</v>
+        <v>0.3223</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9593</v>
+        <v>-0.8532</v>
       </c>
       <c r="P21" t="n">
         <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3901</v>
+        <v>0.0295</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2519</v>
+        <v>-0.1167</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1383</v>
+        <v>0.1462</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0508</v>
+        <v>-0.5767</v>
       </c>
       <c r="W21" t="n">
         <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1168</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1377</v>
+        <v>-2.3012</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8289</v>
+        <v>-2.4843</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3088</v>
+        <v>0.1832</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7937</v>
+        <v>-2.5707</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6459</v>
+        <v>-1.5542</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1478</v>
+        <v>-1.0164</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2628</v>
+        <v>-0.4925</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.4354</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7054</v>
+        <v>-0.0572</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5308</v>
+        <v>-2.0782</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3223</v>
+        <v>-1.1189</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8532</v>
+        <v>-0.9593</v>
       </c>
       <c r="P22" t="n">
         <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9349</v>
+        <v>0.0512</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6524</v>
+        <v>-0.0376</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2824</v>
+        <v>0.0888</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5767</v>
+        <v>1.0508</v>
       </c>
       <c r="W22" t="n">
         <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7442</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2813</v>
+        <v>-2.3779</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.422</v>
+        <v>-1.7469</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8593</v>
+        <v>-0.6309</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0734</v>
+        <v>-2.9847</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9571</v>
+        <v>-0.2007</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1163</v>
+        <v>-2.784</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6482</v>
+        <v>-2.4132</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2598</v>
+        <v>-0.3394</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.908</v>
+        <v>-2.0737</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4252</v>
+        <v>-0.5716</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2169</v>
+        <v>0.1387</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2083</v>
+        <v>-0.7103</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4974</v>
+        <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.548</v>
+        <v>0.1094</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2668</v>
+        <v>0.4363</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8148</v>
+        <v>-0.3268</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1168</v>
+        <v>-1.1675</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1168</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4176</v>
+        <v>-3.1155</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.497</v>
+        <v>-2.7435</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9206</v>
+        <v>-0.372</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9847</v>
+        <v>-4.0734</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2007</v>
+        <v>-0.9571</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.784</v>
+        <v>-3.1163</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4132</v>
+        <v>-1.6482</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3394</v>
+        <v>0.2598</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0737</v>
+        <v>-1.908</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5716</v>
+        <v>-2.4252</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1387</v>
+        <v>-1.2169</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7103</v>
+        <v>-1.2083</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6649</v>
+        <v>2.4974</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9303</v>
+        <v>-0.3822</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3138</v>
+        <v>-0.0547</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6165</v>
+        <v>-0.3275</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1675</v>
+        <v>-0.1168</v>
       </c>
       <c r="W24" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3975</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2887</v>
+        <v>-0.1457999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>9.3324</v>
+        <v>9.3325</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.6212</v>
+        <v>-9.478000000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5719000000000012</v>
+        <v>-0.5719000000000003</v>
       </c>
       <c r="H25" t="n">
         <v>-2.1638</v>
@@ -2383,13 +2383,13 @@
         <v>2.982</v>
       </c>
       <c r="L25" t="n">
-        <v>9.2254</v>
+        <v>9.225399999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-12.7793</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.145799999999999</v>
+        <v>-5.1458</v>
       </c>
       <c r="O25" t="n">
         <v>-7.6334</v>
@@ -2404,13 +2404,13 @@
         <v>17.69</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5689</v>
+        <v>0.5738</v>
       </c>
       <c r="T25" t="n">
         <v>1.9078</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.4769</v>
+        <v>-1.3339</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2289</v>
